--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487539_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487539_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>10.2617</v>
+        <v>9.1633</v>
       </c>
       <c r="E2" t="n">
-        <v>7.6218</v>
+        <v>7.2719</v>
       </c>
       <c r="F2" t="n">
-        <v>2.6399</v>
+        <v>1.8914</v>
       </c>
       <c r="G2" t="n">
         <v>3.0568</v>
@@ -610,13 +610,13 @@
         <v>1.5668</v>
       </c>
       <c r="S2" t="n">
-        <v>1.5977</v>
+        <v>0.4993</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5328000000000001</v>
+        <v>0.1829</v>
       </c>
       <c r="U2" t="n">
-        <v>1.0649</v>
+        <v>0.3164</v>
       </c>
       <c r="V2" t="n">
         <v>4.0403</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.2732</v>
+        <v>7.2185</v>
       </c>
       <c r="E3" t="n">
-        <v>4.5371</v>
+        <v>5.1082</v>
       </c>
       <c r="F3" t="n">
-        <v>1.7361</v>
+        <v>2.1104</v>
       </c>
       <c r="G3" t="n">
         <v>6.3176</v>
@@ -688,13 +688,13 @@
         <v>1.7626</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.4361</v>
+        <v>-0.4908</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.7128</v>
+        <v>-0.1417</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.7233000000000001</v>
+        <v>-0.3491</v>
       </c>
       <c r="V3" t="n">
         <v>0.6083</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. ZORROZUA HERRERO</t>
+          <t>A. MIRANDA GARCIA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.1293</v>
+        <v>2.0578</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5416</v>
+        <v>0.6572</v>
       </c>
       <c r="F4" t="n">
-        <v>1.5878</v>
+        <v>1.4006</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6906</v>
+        <v>0.4093</v>
       </c>
       <c r="H4" t="n">
-        <v>1.8986</v>
+        <v>-0.2225</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.208</v>
+        <v>0.6318</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.07389999999999999</v>
+        <v>0.2646</v>
       </c>
       <c r="K4" t="n">
-        <v>1.9632</v>
+        <v>0.1837</v>
       </c>
       <c r="L4" t="n">
-        <v>-2.0371</v>
+        <v>0.0808</v>
       </c>
       <c r="M4" t="n">
-        <v>0.7645</v>
+        <v>0.1448</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.0646</v>
+        <v>-0.4062</v>
       </c>
       <c r="O4" t="n">
-        <v>0.8290999999999999</v>
+        <v>0.551</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3917</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>-0.9792</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3709</v>
+        <v>0.9792</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7717000000000001</v>
+        <v>0.4318</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7111</v>
+        <v>0.1553</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0606</v>
+        <v>0.2766</v>
       </c>
       <c r="V4" t="n">
-        <v>0.2754</v>
+        <v>1.2166</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8837</v>
+        <v>1.2166</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.6083</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. MIRANDA GARCIA</t>
+          <t>M. ZORROZUA HERRERO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4659</v>
+        <v>1.7422</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1455</v>
+        <v>0.2346</v>
       </c>
       <c r="F5" t="n">
-        <v>1.3204</v>
+        <v>1.5076</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4093</v>
+        <v>0.6906</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.2225</v>
+        <v>1.8986</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6318</v>
+        <v>-1.208</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2646</v>
+        <v>-0.07389999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1837</v>
+        <v>1.9632</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0808</v>
+        <v>-2.0371</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1448</v>
+        <v>0.7645</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.4062</v>
+        <v>-0.0646</v>
       </c>
       <c r="O5" t="n">
-        <v>0.551</v>
+        <v>0.8290999999999999</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>0.3917</v>
       </c>
       <c r="Q5" t="n">
         <v>-0.9792</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9792</v>
+        <v>1.3709</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.16</v>
+        <v>0.3845</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3564</v>
+        <v>0.404</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1964</v>
+        <v>-0.0196</v>
       </c>
       <c r="V5" t="n">
-        <v>1.2166</v>
+        <v>0.2754</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2166</v>
+        <v>0.8837</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.6083</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. ARIAS GONZALEZ</t>
+          <t>J. PEREZ RUIZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2925</v>
+        <v>0.0678</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.4608</v>
+        <v>-1.1684</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7532</v>
+        <v>1.2362</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.315</v>
+        <v>-0.4937</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.6131</v>
+        <v>0.1429</v>
       </c>
       <c r="I6" t="n">
-        <v>1.2981</v>
+        <v>-0.6366000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>0.639</v>
+        <v>-0.3645</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.507</v>
+        <v>0.2773</v>
       </c>
       <c r="L6" t="n">
-        <v>1.1461</v>
+        <v>-0.6418</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.9541</v>
+        <v>-0.1292</v>
       </c>
       <c r="N6" t="n">
-        <v>-2.1061</v>
+        <v>-0.1344</v>
       </c>
       <c r="O6" t="n">
-        <v>0.152</v>
+        <v>0.0052</v>
       </c>
       <c r="P6" t="n">
-        <v>1.9585</v>
+        <v>0.1958</v>
       </c>
       <c r="Q6" t="n">
         <v>-0.9792</v>
       </c>
       <c r="R6" t="n">
-        <v>2.9377</v>
+        <v>1.1751</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.351</v>
+        <v>0.09030000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1206</v>
+        <v>-0.1</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2304</v>
+        <v>0.1903</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.2754</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.2754</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2849</v>
+        <v>0.0562</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.0529</v>
+        <v>-0.9341</v>
       </c>
       <c r="F7" t="n">
-        <v>1.3378</v>
+        <v>0.9903</v>
       </c>
       <c r="G7" t="n">
         <v>0.7289</v>
@@ -1000,13 +1000,13 @@
         <v>2.7419</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1424</v>
+        <v>-0.0863</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6840000000000001</v>
+        <v>-0.5652</v>
       </c>
       <c r="U7" t="n">
-        <v>0.8264</v>
+        <v>0.4789</v>
       </c>
       <c r="V7" t="n">
         <v>-0.3905</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. PEREZ RUIZ</t>
+          <t>J. ARIAS GONZALEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2144</v>
+        <v>-0.1982</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.8614000000000001</v>
+        <v>-1.0583</v>
       </c>
       <c r="F8" t="n">
-        <v>1.0758</v>
+        <v>0.8602</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.4937</v>
+        <v>-1.315</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1429</v>
+        <v>-2.6131</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.6366000000000001</v>
+        <v>1.2981</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.3645</v>
+        <v>0.639</v>
       </c>
       <c r="K8" t="n">
-        <v>0.2773</v>
+        <v>-0.507</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6418</v>
+        <v>1.1461</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.1292</v>
+        <v>-1.9541</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.1344</v>
+        <v>-2.1061</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0052</v>
+        <v>0.152</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1958</v>
+        <v>1.9585</v>
       </c>
       <c r="Q8" t="n">
         <v>-0.9792</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1751</v>
+        <v>2.9377</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2369</v>
+        <v>-0.8416</v>
       </c>
       <c r="T8" t="n">
-        <v>0.207</v>
+        <v>-0.7181</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0299</v>
+        <v>-0.1235</v>
       </c>
       <c r="V8" t="n">
-        <v>0.2754</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2754</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.503</v>
+        <v>-0.3887</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.9489</v>
+        <v>-0.7278</v>
       </c>
       <c r="F9" t="n">
-        <v>0.446</v>
+        <v>0.339</v>
       </c>
       <c r="G9" t="n">
         <v>-1.6244</v>
@@ -1156,13 +1156,13 @@
         <v>1.9585</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.837</v>
+        <v>-0.7228</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.9504</v>
+        <v>-0.7292999999999999</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1134</v>
+        <v>0.0065</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.9177</v>
+        <v>-0.8316</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.4222</v>
+        <v>-1.3628</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5044999999999999</v>
+        <v>0.5312</v>
       </c>
       <c r="G10" t="n">
         <v>-1.3449</v>
@@ -1234,13 +1234,13 @@
         <v>1.3709</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.9438</v>
+        <v>-0.8576</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4158</v>
+        <v>-0.3564</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.528</v>
+        <v>-0.5012</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.9486</v>
+        <v>-1.3255</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.3871</v>
+        <v>-0.9777</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.5616</v>
+        <v>-0.3477</v>
       </c>
       <c r="G11" t="n">
         <v>0.9675</v>
@@ -1312,13 +1312,13 @@
         <v>1.3709</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8367</v>
+        <v>-0.2135</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6534</v>
+        <v>-0.2441</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1833</v>
+        <v>0.0306</v>
       </c>
       <c r="V11" t="n">
         <v>-1.492</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.43</v>
+        <v>-2.1894</v>
       </c>
       <c r="E12" t="n">
         <v>-1.2482</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.1818</v>
+        <v>-0.9412</v>
       </c>
       <c r="G12" t="n">
         <v>-0.8574000000000001</v>
@@ -1390,13 +1390,13 @@
         <v>1.3709</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.0806</v>
+        <v>-0.84</v>
       </c>
       <c r="T12" t="n">
         <v>-0.8316</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.249</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="V12" t="n">
         <v>-0.8837</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.5152</v>
+        <v>-5.171</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.2784</v>
+        <v>-5.0143</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.2368</v>
+        <v>-0.1566</v>
       </c>
       <c r="G13" t="n">
         <v>-3.8791</v>
@@ -1468,13 +1468,13 @@
         <v>1.9585</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.9323</v>
+        <v>-0.588</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.7722</v>
+        <v>-0.5082</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.16</v>
+        <v>-0.0798</v>
       </c>
       <c r="V13" t="n">
         <v>0.2754</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>9.607399999999998</v>
+        <v>10.2014</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1860999999999979</v>
+        <v>0.7802999999999978</v>
       </c>
       <c r="F14" t="n">
-        <v>9.421299999999997</v>
+        <v>9.4214</v>
       </c>
       <c r="G14" t="n">
         <v>2.656199999999999</v>
@@ -1516,10 +1516,10 @@
         <v>0.6873999999999998</v>
       </c>
       <c r="I14" t="n">
-        <v>1.9689</v>
+        <v>1.968899999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>9.656200000000002</v>
+        <v>9.6562</v>
       </c>
       <c r="K14" t="n">
         <v>11.2024</v>
@@ -1546,13 +1546,13 @@
         <v>20.5639</v>
       </c>
       <c r="S14" t="n">
-        <v>-3.8288</v>
+        <v>-3.2347</v>
       </c>
       <c r="T14" t="n">
-        <v>-4.0463</v>
+        <v>-3.4524</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2175999999999998</v>
+        <v>0.2177</v>
       </c>
       <c r="V14" t="n">
         <v>3.9252</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Y. PINAS</t>
+          <t>P. BADDINI GABRIOTTI RODRIGUES</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.3123</v>
+        <v>2.8225</v>
       </c>
       <c r="E15" t="n">
-        <v>3.4484</v>
+        <v>0.5147</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.1362</v>
+        <v>2.3078</v>
       </c>
       <c r="G15" t="n">
-        <v>3.0157</v>
+        <v>0.0177</v>
       </c>
       <c r="H15" t="n">
-        <v>4.0357</v>
+        <v>0.2246</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.02</v>
+        <v>-0.2069</v>
       </c>
       <c r="J15" t="n">
-        <v>4.4824</v>
+        <v>0.4688</v>
       </c>
       <c r="K15" t="n">
-        <v>4.4419</v>
+        <v>1.1058</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0404</v>
+        <v>-0.637</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.4667</v>
+        <v>-0.4511</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.4062</v>
+        <v>-0.8812</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.0604</v>
+        <v>0.4301</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.5875</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>-1.9585</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3709</v>
+        <v>1.9585</v>
       </c>
       <c r="S15" t="n">
-        <v>2.1007</v>
+        <v>1.0375</v>
       </c>
       <c r="T15" t="n">
-        <v>0.9245</v>
+        <v>-0.0382</v>
       </c>
       <c r="U15" t="n">
-        <v>1.1762</v>
+        <v>1.0757</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.2166</v>
+        <v>1.7673</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>2.0427</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.2166</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>P. BADDINI GABRIOTTI RODRIGUES</t>
+          <t>Y. PINAS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.8179</v>
+        <v>2.796</v>
       </c>
       <c r="E16" t="n">
-        <v>0.617</v>
+        <v>3.0391</v>
       </c>
       <c r="F16" t="n">
-        <v>2.2008</v>
+        <v>-0.2431</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0177</v>
+        <v>3.0157</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2246</v>
+        <v>4.0357</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.2069</v>
+        <v>-1.02</v>
       </c>
       <c r="J16" t="n">
-        <v>0.4688</v>
+        <v>4.4824</v>
       </c>
       <c r="K16" t="n">
-        <v>1.1058</v>
+        <v>4.4419</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.637</v>
+        <v>0.0404</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.4511</v>
+        <v>-1.4667</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.8812</v>
+        <v>-0.4062</v>
       </c>
       <c r="O16" t="n">
-        <v>0.4301</v>
+        <v>-1.0604</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>-0.5875</v>
       </c>
       <c r="Q16" t="n">
         <v>-1.9585</v>
       </c>
       <c r="R16" t="n">
-        <v>1.9585</v>
+        <v>1.3709</v>
       </c>
       <c r="S16" t="n">
-        <v>1.0329</v>
+        <v>1.5844</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0641</v>
+        <v>0.5152</v>
       </c>
       <c r="U16" t="n">
-        <v>0.9688</v>
+        <v>1.0692</v>
       </c>
       <c r="V16" t="n">
-        <v>1.7673</v>
+        <v>-1.2166</v>
       </c>
       <c r="W16" t="n">
-        <v>2.0427</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.2754</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. MASEDA SOILAN</t>
+          <t>S. RODRÍGUEZ TAPIA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.7917</v>
+        <v>1.5275</v>
       </c>
       <c r="E17" t="n">
-        <v>0.4809</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>1.3108</v>
+        <v>1.4561</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.6747</v>
+        <v>2.1045</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.8167</v>
+        <v>-0.0731</v>
       </c>
       <c r="I17" t="n">
-        <v>1.142</v>
+        <v>2.1776</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.4965</v>
+        <v>2.2993</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.072</v>
+        <v>1.082</v>
       </c>
       <c r="L17" t="n">
-        <v>0.5755</v>
+        <v>1.2173</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.1782</v>
+        <v>-0.1948</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.7447</v>
+        <v>-1.1551</v>
       </c>
       <c r="O17" t="n">
-        <v>0.5666</v>
+        <v>0.9603</v>
       </c>
       <c r="P17" t="n">
-        <v>1.9585</v>
+        <v>-0.3917</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.1958</v>
+        <v>-1.9585</v>
       </c>
       <c r="R17" t="n">
-        <v>2.1543</v>
+        <v>1.5668</v>
       </c>
       <c r="S17" t="n">
-        <v>1.9999</v>
+        <v>0.423</v>
       </c>
       <c r="T17" t="n">
-        <v>1.1733</v>
+        <v>-0.2694</v>
       </c>
       <c r="U17" t="n">
-        <v>0.8266</v>
+        <v>0.6924</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.492</v>
+        <v>-0.6083</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.492</v>
+        <v>-0.6083</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S. RODRÍGUEZ TAPIA</t>
+          <t>D. MASEDA SOILAN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.2472</v>
+        <v>0.9196</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.2356</v>
+        <v>-0.3377</v>
       </c>
       <c r="F18" t="n">
-        <v>1.4828</v>
+        <v>1.2573</v>
       </c>
       <c r="G18" t="n">
-        <v>2.1045</v>
+        <v>-0.6747</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.0731</v>
+        <v>-1.8167</v>
       </c>
       <c r="I18" t="n">
-        <v>2.1776</v>
+        <v>1.142</v>
       </c>
       <c r="J18" t="n">
-        <v>2.2993</v>
+        <v>-0.4965</v>
       </c>
       <c r="K18" t="n">
-        <v>1.082</v>
+        <v>-1.072</v>
       </c>
       <c r="L18" t="n">
-        <v>1.2173</v>
+        <v>0.5755</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.1948</v>
+        <v>-0.1782</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.1551</v>
+        <v>-0.7447</v>
       </c>
       <c r="O18" t="n">
-        <v>0.9603</v>
+        <v>0.5666</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.3917</v>
+        <v>1.9585</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.9585</v>
+        <v>-0.1958</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5668</v>
+        <v>2.1543</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1427</v>
+        <v>1.1278</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5764</v>
+        <v>0.3546</v>
       </c>
       <c r="U18" t="n">
-        <v>0.7191</v>
+        <v>0.7731</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.6083</v>
+        <v>-1.492</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.6083</v>
+        <v>-1.492</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.199</v>
+        <v>-0.656</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.3301</v>
+        <v>-2.9208</v>
       </c>
       <c r="F19" t="n">
-        <v>2.1311</v>
+        <v>2.2648</v>
       </c>
       <c r="G19" t="n">
         <v>1.2932</v>
@@ -1936,13 +1936,13 @@
         <v>1.3709</v>
       </c>
       <c r="S19" t="n">
-        <v>0.2497</v>
+        <v>0.7927</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.22</v>
+        <v>0.1894</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4696</v>
+        <v>0.6032999999999999</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.6317</v>
+        <v>-1.7165</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.3536</v>
+        <v>-1.2513</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2781</v>
+        <v>-0.4652</v>
       </c>
       <c r="G20" t="n">
         <v>-1.4522</v>
@@ -2014,13 +2014,13 @@
         <v>0.5875</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6288</v>
+        <v>-0.7136</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5764</v>
+        <v>-0.474</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0524</v>
+        <v>-0.2395</v>
       </c>
       <c r="V20" t="n">
         <v>0.0576</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. QITTANE</t>
+          <t>H. MATEO MERELLES</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.0768</v>
+        <v>-1.7872</v>
       </c>
       <c r="E21" t="n">
-        <v>0.8826000000000001</v>
+        <v>-1.2942</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.9594</v>
+        <v>-0.4931</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.3818</v>
+        <v>-1.7864</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.1045</v>
+        <v>-0.0333</v>
       </c>
       <c r="I21" t="n">
-        <v>0.7227</v>
+        <v>-1.7531</v>
       </c>
       <c r="J21" t="n">
-        <v>1.8482</v>
+        <v>-0.5802</v>
       </c>
       <c r="K21" t="n">
-        <v>0.5954</v>
+        <v>0.1021</v>
       </c>
       <c r="L21" t="n">
-        <v>1.2529</v>
+        <v>-0.6822</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.2301</v>
+        <v>-1.2062</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.6999</v>
+        <v>-0.1354</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.5302</v>
+        <v>-1.0708</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.5875</v>
+        <v>-0.3917</v>
       </c>
       <c r="Q21" t="n">
         <v>-0.9792</v>
       </c>
       <c r="R21" t="n">
-        <v>0.3917</v>
+        <v>0.5875</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1661</v>
+        <v>0.6662</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2617</v>
+        <v>0.2652</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0956</v>
+        <v>0.401</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.9412</v>
+        <v>-0.2754</v>
       </c>
       <c r="W21" t="n">
-        <v>0.2754</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.2166</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Q. HUANG</t>
+          <t>M. QITTANE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.0908</v>
+        <v>-1.9034</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.4378</v>
+        <v>1.1896</v>
       </c>
       <c r="F22" t="n">
-        <v>0.347</v>
+        <v>-3.0931</v>
       </c>
       <c r="G22" t="n">
-        <v>1.9057</v>
+        <v>-0.3818</v>
       </c>
       <c r="H22" t="n">
-        <v>1.097</v>
+        <v>-1.1045</v>
       </c>
       <c r="I22" t="n">
-        <v>0.8087</v>
+        <v>0.7227</v>
       </c>
       <c r="J22" t="n">
-        <v>2.3702</v>
+        <v>1.8482</v>
       </c>
       <c r="K22" t="n">
-        <v>2.9312</v>
+        <v>0.5954</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.5610000000000001</v>
+        <v>1.2529</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.4646</v>
+        <v>-2.2301</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.8342</v>
+        <v>-1.6999</v>
       </c>
       <c r="O22" t="n">
-        <v>1.3697</v>
+        <v>-0.5302</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.7419</v>
+        <v>-0.5875</v>
       </c>
       <c r="Q22" t="n">
-        <v>-4.1128</v>
+        <v>-0.9792</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3709</v>
+        <v>0.3917</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.6462</v>
+        <v>0.0072</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6952</v>
+        <v>0.0453</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0489</v>
+        <v>-0.0381</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.6083</v>
+        <v>-0.9412</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.2754</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.6083</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>H. MATEO MERELLES</t>
+          <t>Q. HUANG</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.121</v>
+        <v>-2.0465</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.6012</v>
+        <v>-2.2331</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.5198</v>
+        <v>0.1866</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.7864</v>
+        <v>1.9057</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.0333</v>
+        <v>1.097</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.7531</v>
+        <v>0.8087</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.5802</v>
+        <v>2.3702</v>
       </c>
       <c r="K23" t="n">
-        <v>0.1021</v>
+        <v>2.9312</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.6822</v>
+        <v>-0.5610000000000001</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.2062</v>
+        <v>-0.4646</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.1354</v>
+        <v>-1.8342</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.0708</v>
+        <v>1.3697</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.3917</v>
+        <v>-2.7419</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.9792</v>
+        <v>-4.1128</v>
       </c>
       <c r="R23" t="n">
-        <v>0.5875</v>
+        <v>1.3709</v>
       </c>
       <c r="S23" t="n">
-        <v>0.3325</v>
+        <v>-0.602</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.0418</v>
+        <v>-0.4905</v>
       </c>
       <c r="U23" t="n">
-        <v>0.3742</v>
+        <v>-0.1114</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.2754</v>
+        <v>-0.6083</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.2754</v>
+        <v>-0.6083</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.2041</v>
+        <v>-4.4217</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.6804</v>
+        <v>-4.1921</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.5237000000000001</v>
+        <v>-0.2297</v>
       </c>
       <c r="G24" t="n">
         <v>-4.4466</v>
@@ -2326,13 +2326,13 @@
         <v>1.7626</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.3451</v>
+        <v>-0.5627</v>
       </c>
       <c r="T24" t="n">
-        <v>0.1941</v>
+        <v>-0.3176</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.5391</v>
+        <v>-0.2451</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.4532</v>
+        <v>-5.1416</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.2116</v>
+        <v>-2.007</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.2416</v>
+        <v>-3.1346</v>
       </c>
       <c r="G25" t="n">
         <v>-2.2513</v>
@@ -2404,13 +2404,13 @@
         <v>0.5875</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.2434</v>
+        <v>0.0682</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.2023</v>
+        <v>0.0023</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.041</v>
+        <v>0.0659</v>
       </c>
       <c r="V25" t="n">
         <v>-0.6083</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-9.607500000000002</v>
+        <v>-9.607300000000002</v>
       </c>
       <c r="E26" t="n">
-        <v>-9.421399999999998</v>
+        <v>-9.4214</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.1863000000000001</v>
+        <v>-0.1861999999999995</v>
       </c>
       <c r="G26" t="n">
         <v>-2.656200000000001</v>
@@ -2455,7 +2455,7 @@
         <v>-1.9688</v>
       </c>
       <c r="J26" t="n">
-        <v>6.999899999999999</v>
+        <v>6.999900000000001</v>
       </c>
       <c r="K26" t="n">
         <v>10.5149</v>
@@ -2473,7 +2473,7 @@
         <v>1.5463</v>
       </c>
       <c r="P26" t="n">
-        <v>-6.854699999999998</v>
+        <v>-6.854699999999999</v>
       </c>
       <c r="Q26" t="n">
         <v>-20.5639</v>
@@ -2482,13 +2482,13 @@
         <v>13.7091</v>
       </c>
       <c r="S26" t="n">
-        <v>3.828799999999999</v>
+        <v>3.8287</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.2178</v>
+        <v>-0.2176999999999999</v>
       </c>
       <c r="U26" t="n">
-        <v>4.046499999999999</v>
+        <v>4.0465</v>
       </c>
       <c r="V26" t="n">
         <v>-3.925199999999999</v>
@@ -2497,7 +2497,7 @@
         <v>4.3608</v>
       </c>
       <c r="X26" t="n">
-        <v>-8.286000000000001</v>
+        <v>-8.286</v>
       </c>
     </row>
   </sheetData>
